--- a/web/public/forms/wolgan-bogoseo.xlsx
+++ b/web/public/forms/wolgan-bogoseo.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월간 공사추진현황 보고서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'월간 공사추진현황 보고서'!$A$1:$X$64</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'월간 공사추진현황 보고서'!$A$1:$X$67</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0;&quot;&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,29 +37,50 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -65,12 +92,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF3FB"/>
+        <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,23 +111,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,32 +136,53 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -501,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X67"/>
+  <dimension ref="A1:X70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.6" customWidth="1" min="1" max="1"/>
@@ -530,15 +578,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -562,7 +610,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -592,7 +640,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -622,7 +670,7 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="5" t="n"/>
       <c r="I7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
@@ -652,7 +700,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -682,7 +730,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="8" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -713,7 +761,7 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -732,7 +780,7 @@
       <c r="W11" s="5" t="n"/>
       <c r="X11" s="5" t="n"/>
     </row>
-    <row r="12" ht="24" customHeight="1">
+    <row r="12" ht="34" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  공정률 (계획 / 실적)</t>
@@ -743,7 +791,7 @@
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="n"/>
       <c r="H12" s="5" t="n"/>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
@@ -773,7 +821,7 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="5" t="n"/>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
@@ -794,7 +842,7 @@
     </row>
     <row r="14" ht="6" customHeight="1"/>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>■ 당월 주요 시공 실적</t>
         </is>
@@ -802,7 +850,7 @@
     </row>
     <row r="16" ht="6" customHeight="1"/>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>공종</t>
         </is>
@@ -810,7 +858,7 @@
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="5" t="n"/>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>시공 내용</t>
         </is>
@@ -823,14 +871,14 @@
       <c r="K17" s="5" t="n"/>
       <c r="L17" s="5" t="n"/>
       <c r="M17" s="5" t="n"/>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="Q17" s="10" t="inlineStr">
         <is>
           <t>기간</t>
         </is>
@@ -838,7 +886,7 @@
       <c r="R17" s="5" t="n"/>
       <c r="S17" s="5" t="n"/>
       <c r="T17" s="5" t="n"/>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="U17" s="10" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -848,11 +896,11 @@
       <c r="X17" s="5" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="9" t="inlineStr"/>
+      <c r="A18" s="11" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="5" t="n"/>
-      <c r="E18" s="9" t="inlineStr"/>
+      <c r="E18" s="12" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
@@ -861,24 +909,24 @@
       <c r="K18" s="5" t="n"/>
       <c r="L18" s="5" t="n"/>
       <c r="M18" s="5" t="n"/>
-      <c r="N18" s="9" t="inlineStr"/>
+      <c r="N18" s="11" t="n"/>
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="9" t="inlineStr"/>
+      <c r="Q18" s="11" t="n"/>
       <c r="R18" s="5" t="n"/>
       <c r="S18" s="5" t="n"/>
       <c r="T18" s="5" t="n"/>
-      <c r="U18" s="9" t="inlineStr"/>
+      <c r="U18" s="11" t="n"/>
       <c r="V18" s="5" t="n"/>
       <c r="W18" s="5" t="n"/>
       <c r="X18" s="5" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="9" t="inlineStr"/>
+      <c r="A19" s="11" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="5" t="n"/>
-      <c r="E19" s="9" t="inlineStr"/>
+      <c r="E19" s="12" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
@@ -887,24 +935,24 @@
       <c r="K19" s="5" t="n"/>
       <c r="L19" s="5" t="n"/>
       <c r="M19" s="5" t="n"/>
-      <c r="N19" s="9" t="inlineStr"/>
+      <c r="N19" s="11" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="9" t="inlineStr"/>
+      <c r="Q19" s="11" t="n"/>
       <c r="R19" s="5" t="n"/>
       <c r="S19" s="5" t="n"/>
       <c r="T19" s="5" t="n"/>
-      <c r="U19" s="9" t="inlineStr"/>
+      <c r="U19" s="11" t="n"/>
       <c r="V19" s="5" t="n"/>
       <c r="W19" s="5" t="n"/>
       <c r="X19" s="5" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="inlineStr"/>
+      <c r="A20" s="11" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="9" t="inlineStr"/>
+      <c r="E20" s="12" t="n"/>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
@@ -913,24 +961,24 @@
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
       <c r="M20" s="5" t="n"/>
-      <c r="N20" s="9" t="inlineStr"/>
+      <c r="N20" s="11" t="n"/>
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="9" t="inlineStr"/>
+      <c r="Q20" s="11" t="n"/>
       <c r="R20" s="5" t="n"/>
       <c r="S20" s="5" t="n"/>
       <c r="T20" s="5" t="n"/>
-      <c r="U20" s="9" t="inlineStr"/>
+      <c r="U20" s="11" t="n"/>
       <c r="V20" s="5" t="n"/>
       <c r="W20" s="5" t="n"/>
       <c r="X20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="9" t="inlineStr"/>
+      <c r="A21" s="11" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
       <c r="D21" s="5" t="n"/>
-      <c r="E21" s="9" t="inlineStr"/>
+      <c r="E21" s="12" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
@@ -939,24 +987,24 @@
       <c r="K21" s="5" t="n"/>
       <c r="L21" s="5" t="n"/>
       <c r="M21" s="5" t="n"/>
-      <c r="N21" s="9" t="inlineStr"/>
+      <c r="N21" s="11" t="n"/>
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="9" t="inlineStr"/>
+      <c r="Q21" s="11" t="n"/>
       <c r="R21" s="5" t="n"/>
       <c r="S21" s="5" t="n"/>
       <c r="T21" s="5" t="n"/>
-      <c r="U21" s="9" t="inlineStr"/>
+      <c r="U21" s="11" t="n"/>
       <c r="V21" s="5" t="n"/>
       <c r="W21" s="5" t="n"/>
       <c r="X21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="9" t="inlineStr"/>
+      <c r="A22" s="11" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="5" t="n"/>
       <c r="D22" s="5" t="n"/>
-      <c r="E22" s="9" t="inlineStr"/>
+      <c r="E22" s="12" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
@@ -965,24 +1013,24 @@
       <c r="K22" s="5" t="n"/>
       <c r="L22" s="5" t="n"/>
       <c r="M22" s="5" t="n"/>
-      <c r="N22" s="9" t="inlineStr"/>
+      <c r="N22" s="11" t="n"/>
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="9" t="inlineStr"/>
+      <c r="Q22" s="11" t="n"/>
       <c r="R22" s="5" t="n"/>
       <c r="S22" s="5" t="n"/>
       <c r="T22" s="5" t="n"/>
-      <c r="U22" s="9" t="inlineStr"/>
+      <c r="U22" s="11" t="n"/>
       <c r="V22" s="5" t="n"/>
       <c r="W22" s="5" t="n"/>
       <c r="X22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="9" t="inlineStr"/>
+      <c r="A23" s="11" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
       <c r="D23" s="5" t="n"/>
-      <c r="E23" s="9" t="inlineStr"/>
+      <c r="E23" s="12" t="n"/>
       <c r="F23" s="5" t="n"/>
       <c r="G23" s="5" t="n"/>
       <c r="H23" s="5" t="n"/>
@@ -991,24 +1039,24 @@
       <c r="K23" s="5" t="n"/>
       <c r="L23" s="5" t="n"/>
       <c r="M23" s="5" t="n"/>
-      <c r="N23" s="9" t="inlineStr"/>
+      <c r="N23" s="11" t="n"/>
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="9" t="inlineStr"/>
+      <c r="Q23" s="11" t="n"/>
       <c r="R23" s="5" t="n"/>
       <c r="S23" s="5" t="n"/>
       <c r="T23" s="5" t="n"/>
-      <c r="U23" s="9" t="inlineStr"/>
+      <c r="U23" s="11" t="n"/>
       <c r="V23" s="5" t="n"/>
       <c r="W23" s="5" t="n"/>
       <c r="X23" s="5" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="9" t="inlineStr"/>
+      <c r="A24" s="11" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="5" t="n"/>
-      <c r="E24" s="9" t="inlineStr"/>
+      <c r="E24" s="12" t="n"/>
       <c r="F24" s="5" t="n"/>
       <c r="G24" s="5" t="n"/>
       <c r="H24" s="5" t="n"/>
@@ -1017,24 +1065,24 @@
       <c r="K24" s="5" t="n"/>
       <c r="L24" s="5" t="n"/>
       <c r="M24" s="5" t="n"/>
-      <c r="N24" s="9" t="inlineStr"/>
+      <c r="N24" s="11" t="n"/>
       <c r="O24" s="5" t="n"/>
       <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="9" t="inlineStr"/>
+      <c r="Q24" s="11" t="n"/>
       <c r="R24" s="5" t="n"/>
       <c r="S24" s="5" t="n"/>
       <c r="T24" s="5" t="n"/>
-      <c r="U24" s="9" t="inlineStr"/>
+      <c r="U24" s="11" t="n"/>
       <c r="V24" s="5" t="n"/>
       <c r="W24" s="5" t="n"/>
       <c r="X24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="9" t="inlineStr"/>
+      <c r="A25" s="11" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="5" t="n"/>
-      <c r="E25" s="9" t="inlineStr"/>
+      <c r="E25" s="12" t="n"/>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="5" t="n"/>
       <c r="H25" s="5" t="n"/>
@@ -1043,21 +1091,21 @@
       <c r="K25" s="5" t="n"/>
       <c r="L25" s="5" t="n"/>
       <c r="M25" s="5" t="n"/>
-      <c r="N25" s="9" t="inlineStr"/>
+      <c r="N25" s="11" t="n"/>
       <c r="O25" s="5" t="n"/>
       <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="9" t="inlineStr"/>
+      <c r="Q25" s="11" t="n"/>
       <c r="R25" s="5" t="n"/>
       <c r="S25" s="5" t="n"/>
       <c r="T25" s="5" t="n"/>
-      <c r="U25" s="9" t="inlineStr"/>
+      <c r="U25" s="11" t="n"/>
       <c r="V25" s="5" t="n"/>
       <c r="W25" s="5" t="n"/>
       <c r="X25" s="5" t="n"/>
     </row>
     <row r="26" ht="6" customHeight="1"/>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>■ 익월 시공 계획</t>
         </is>
@@ -1065,7 +1113,7 @@
     </row>
     <row r="28" ht="6" customHeight="1"/>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>공종</t>
         </is>
@@ -1073,7 +1121,7 @@
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
       <c r="D29" s="5" t="n"/>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E29" s="10" t="inlineStr">
         <is>
           <t>시공 내용</t>
         </is>
@@ -1086,14 +1134,14 @@
       <c r="K29" s="5" t="n"/>
       <c r="L29" s="5" t="n"/>
       <c r="M29" s="5" t="n"/>
-      <c r="N29" s="8" t="inlineStr">
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>수량</t>
         </is>
       </c>
       <c r="O29" s="5" t="n"/>
       <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="8" t="inlineStr">
+      <c r="Q29" s="10" t="inlineStr">
         <is>
           <t>기간</t>
         </is>
@@ -1101,7 +1149,7 @@
       <c r="R29" s="5" t="n"/>
       <c r="S29" s="5" t="n"/>
       <c r="T29" s="5" t="n"/>
-      <c r="U29" s="8" t="inlineStr">
+      <c r="U29" s="10" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1111,11 +1159,11 @@
       <c r="X29" s="5" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="9" t="inlineStr"/>
+      <c r="A30" s="11" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="5" t="n"/>
       <c r="D30" s="5" t="n"/>
-      <c r="E30" s="9" t="inlineStr"/>
+      <c r="E30" s="12" t="n"/>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n"/>
       <c r="H30" s="5" t="n"/>
@@ -1124,24 +1172,24 @@
       <c r="K30" s="5" t="n"/>
       <c r="L30" s="5" t="n"/>
       <c r="M30" s="5" t="n"/>
-      <c r="N30" s="9" t="inlineStr"/>
+      <c r="N30" s="11" t="n"/>
       <c r="O30" s="5" t="n"/>
       <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="9" t="inlineStr"/>
+      <c r="Q30" s="11" t="n"/>
       <c r="R30" s="5" t="n"/>
       <c r="S30" s="5" t="n"/>
       <c r="T30" s="5" t="n"/>
-      <c r="U30" s="9" t="inlineStr"/>
+      <c r="U30" s="11" t="n"/>
       <c r="V30" s="5" t="n"/>
       <c r="W30" s="5" t="n"/>
       <c r="X30" s="5" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="9" t="inlineStr"/>
+      <c r="A31" s="11" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="5" t="n"/>
       <c r="D31" s="5" t="n"/>
-      <c r="E31" s="9" t="inlineStr"/>
+      <c r="E31" s="12" t="n"/>
       <c r="F31" s="5" t="n"/>
       <c r="G31" s="5" t="n"/>
       <c r="H31" s="5" t="n"/>
@@ -1150,24 +1198,24 @@
       <c r="K31" s="5" t="n"/>
       <c r="L31" s="5" t="n"/>
       <c r="M31" s="5" t="n"/>
-      <c r="N31" s="9" t="inlineStr"/>
+      <c r="N31" s="11" t="n"/>
       <c r="O31" s="5" t="n"/>
       <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="9" t="inlineStr"/>
+      <c r="Q31" s="11" t="n"/>
       <c r="R31" s="5" t="n"/>
       <c r="S31" s="5" t="n"/>
       <c r="T31" s="5" t="n"/>
-      <c r="U31" s="9" t="inlineStr"/>
+      <c r="U31" s="11" t="n"/>
       <c r="V31" s="5" t="n"/>
       <c r="W31" s="5" t="n"/>
       <c r="X31" s="5" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="inlineStr"/>
+      <c r="A32" s="11" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
       <c r="D32" s="5" t="n"/>
-      <c r="E32" s="9" t="inlineStr"/>
+      <c r="E32" s="12" t="n"/>
       <c r="F32" s="5" t="n"/>
       <c r="G32" s="5" t="n"/>
       <c r="H32" s="5" t="n"/>
@@ -1176,24 +1224,24 @@
       <c r="K32" s="5" t="n"/>
       <c r="L32" s="5" t="n"/>
       <c r="M32" s="5" t="n"/>
-      <c r="N32" s="9" t="inlineStr"/>
+      <c r="N32" s="11" t="n"/>
       <c r="O32" s="5" t="n"/>
       <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="9" t="inlineStr"/>
+      <c r="Q32" s="11" t="n"/>
       <c r="R32" s="5" t="n"/>
       <c r="S32" s="5" t="n"/>
       <c r="T32" s="5" t="n"/>
-      <c r="U32" s="9" t="inlineStr"/>
+      <c r="U32" s="11" t="n"/>
       <c r="V32" s="5" t="n"/>
       <c r="W32" s="5" t="n"/>
       <c r="X32" s="5" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="inlineStr"/>
+      <c r="A33" s="11" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="5" t="n"/>
       <c r="D33" s="5" t="n"/>
-      <c r="E33" s="9" t="inlineStr"/>
+      <c r="E33" s="12" t="n"/>
       <c r="F33" s="5" t="n"/>
       <c r="G33" s="5" t="n"/>
       <c r="H33" s="5" t="n"/>
@@ -1202,24 +1250,24 @@
       <c r="K33" s="5" t="n"/>
       <c r="L33" s="5" t="n"/>
       <c r="M33" s="5" t="n"/>
-      <c r="N33" s="9" t="inlineStr"/>
+      <c r="N33" s="11" t="n"/>
       <c r="O33" s="5" t="n"/>
       <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="9" t="inlineStr"/>
+      <c r="Q33" s="11" t="n"/>
       <c r="R33" s="5" t="n"/>
       <c r="S33" s="5" t="n"/>
       <c r="T33" s="5" t="n"/>
-      <c r="U33" s="9" t="inlineStr"/>
+      <c r="U33" s="11" t="n"/>
       <c r="V33" s="5" t="n"/>
       <c r="W33" s="5" t="n"/>
       <c r="X33" s="5" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="inlineStr"/>
+      <c r="A34" s="11" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
       <c r="D34" s="5" t="n"/>
-      <c r="E34" s="9" t="inlineStr"/>
+      <c r="E34" s="12" t="n"/>
       <c r="F34" s="5" t="n"/>
       <c r="G34" s="5" t="n"/>
       <c r="H34" s="5" t="n"/>
@@ -1228,24 +1276,24 @@
       <c r="K34" s="5" t="n"/>
       <c r="L34" s="5" t="n"/>
       <c r="M34" s="5" t="n"/>
-      <c r="N34" s="9" t="inlineStr"/>
+      <c r="N34" s="11" t="n"/>
       <c r="O34" s="5" t="n"/>
       <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="9" t="inlineStr"/>
+      <c r="Q34" s="11" t="n"/>
       <c r="R34" s="5" t="n"/>
       <c r="S34" s="5" t="n"/>
       <c r="T34" s="5" t="n"/>
-      <c r="U34" s="9" t="inlineStr"/>
+      <c r="U34" s="11" t="n"/>
       <c r="V34" s="5" t="n"/>
       <c r="W34" s="5" t="n"/>
       <c r="X34" s="5" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="inlineStr"/>
+      <c r="A35" s="11" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
       <c r="D35" s="5" t="n"/>
-      <c r="E35" s="9" t="inlineStr"/>
+      <c r="E35" s="12" t="n"/>
       <c r="F35" s="5" t="n"/>
       <c r="G35" s="5" t="n"/>
       <c r="H35" s="5" t="n"/>
@@ -1254,24 +1302,24 @@
       <c r="K35" s="5" t="n"/>
       <c r="L35" s="5" t="n"/>
       <c r="M35" s="5" t="n"/>
-      <c r="N35" s="9" t="inlineStr"/>
+      <c r="N35" s="11" t="n"/>
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="9" t="inlineStr"/>
+      <c r="Q35" s="11" t="n"/>
       <c r="R35" s="5" t="n"/>
       <c r="S35" s="5" t="n"/>
       <c r="T35" s="5" t="n"/>
-      <c r="U35" s="9" t="inlineStr"/>
+      <c r="U35" s="11" t="n"/>
       <c r="V35" s="5" t="n"/>
       <c r="W35" s="5" t="n"/>
       <c r="X35" s="5" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="inlineStr"/>
+      <c r="A36" s="11" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
       <c r="D36" s="5" t="n"/>
-      <c r="E36" s="9" t="inlineStr"/>
+      <c r="E36" s="12" t="n"/>
       <c r="F36" s="5" t="n"/>
       <c r="G36" s="5" t="n"/>
       <c r="H36" s="5" t="n"/>
@@ -1280,24 +1328,24 @@
       <c r="K36" s="5" t="n"/>
       <c r="L36" s="5" t="n"/>
       <c r="M36" s="5" t="n"/>
-      <c r="N36" s="9" t="inlineStr"/>
+      <c r="N36" s="11" t="n"/>
       <c r="O36" s="5" t="n"/>
       <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="9" t="inlineStr"/>
+      <c r="Q36" s="11" t="n"/>
       <c r="R36" s="5" t="n"/>
       <c r="S36" s="5" t="n"/>
       <c r="T36" s="5" t="n"/>
-      <c r="U36" s="9" t="inlineStr"/>
+      <c r="U36" s="11" t="n"/>
       <c r="V36" s="5" t="n"/>
       <c r="W36" s="5" t="n"/>
       <c r="X36" s="5" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="9" t="inlineStr"/>
+      <c r="A37" s="11" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="5" t="n"/>
-      <c r="E37" s="9" t="inlineStr"/>
+      <c r="E37" s="12" t="n"/>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n"/>
       <c r="H37" s="5" t="n"/>
@@ -1306,21 +1354,1635 @@
       <c r="K37" s="5" t="n"/>
       <c r="L37" s="5" t="n"/>
       <c r="M37" s="5" t="n"/>
-      <c r="N37" s="9" t="inlineStr"/>
+      <c r="N37" s="11" t="n"/>
       <c r="O37" s="5" t="n"/>
       <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="9" t="inlineStr"/>
+      <c r="Q37" s="11" t="n"/>
       <c r="R37" s="5" t="n"/>
       <c r="S37" s="5" t="n"/>
       <c r="T37" s="5" t="n"/>
-      <c r="U37" s="9" t="inlineStr"/>
+      <c r="U37" s="11" t="n"/>
       <c r="V37" s="5" t="n"/>
       <c r="W37" s="5" t="n"/>
       <c r="X37" s="5" t="n"/>
     </row>
     <row r="38" ht="6" customHeight="1"/>
+    <row r="39" ht="6.666666666666667" customHeight="1"/>
+    <row r="40" ht="6.666666666666667" customHeight="1"/>
+    <row r="41" ht="6.666666666666667" customHeight="1"/>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>■ 인원·장비 / 안전·품질</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="10" t="inlineStr">
+        <is>
+          <t>수량·건수</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="n"/>
+      <c r="R44" s="5" t="n"/>
+      <c r="S44" s="5" t="n"/>
+      <c r="T44" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="n"/>
+      <c r="V44" s="5" t="n"/>
+      <c r="W44" s="5" t="n"/>
+      <c r="X44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="11" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="11" t="n"/>
+      <c r="Q45" s="5" t="n"/>
+      <c r="R45" s="5" t="n"/>
+      <c r="S45" s="5" t="n"/>
+      <c r="T45" s="11" t="n"/>
+      <c r="U45" s="5" t="n"/>
+      <c r="V45" s="5" t="n"/>
+      <c r="W45" s="5" t="n"/>
+      <c r="X45" s="5" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="11" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="11" t="n"/>
+      <c r="Q46" s="5" t="n"/>
+      <c r="R46" s="5" t="n"/>
+      <c r="S46" s="5" t="n"/>
+      <c r="T46" s="11" t="n"/>
+      <c r="U46" s="5" t="n"/>
+      <c r="V46" s="5" t="n"/>
+      <c r="W46" s="5" t="n"/>
+      <c r="X46" s="5" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="11" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="5" t="n"/>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="11" t="n"/>
+      <c r="Q47" s="5" t="n"/>
+      <c r="R47" s="5" t="n"/>
+      <c r="S47" s="5" t="n"/>
+      <c r="T47" s="11" t="n"/>
+      <c r="U47" s="5" t="n"/>
+      <c r="V47" s="5" t="n"/>
+      <c r="W47" s="5" t="n"/>
+      <c r="X47" s="5" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="11" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="11" t="n"/>
+      <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n"/>
+      <c r="T48" s="11" t="n"/>
+      <c r="U48" s="5" t="n"/>
+      <c r="V48" s="5" t="n"/>
+      <c r="W48" s="5" t="n"/>
+      <c r="X48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="5" t="n"/>
+      <c r="J49" s="5" t="n"/>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="11" t="n"/>
+      <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="5" t="n"/>
+      <c r="S49" s="5" t="n"/>
+      <c r="T49" s="11" t="n"/>
+      <c r="U49" s="5" t="n"/>
+      <c r="V49" s="5" t="n"/>
+      <c r="W49" s="5" t="n"/>
+      <c r="X49" s="5" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="11" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="5" t="n"/>
+      <c r="J50" s="5" t="n"/>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="11" t="n"/>
+      <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="5" t="n"/>
+      <c r="S50" s="5" t="n"/>
+      <c r="T50" s="11" t="n"/>
+      <c r="U50" s="5" t="n"/>
+      <c r="V50" s="5" t="n"/>
+      <c r="W50" s="5" t="n"/>
+      <c r="X50" s="5" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="11" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="5" t="n"/>
+      <c r="S51" s="5" t="n"/>
+      <c r="T51" s="11" t="n"/>
+      <c r="U51" s="5" t="n"/>
+      <c r="V51" s="5" t="n"/>
+      <c r="W51" s="5" t="n"/>
+      <c r="X51" s="5" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="5" t="n"/>
+      <c r="R52" s="5" t="n"/>
+      <c r="S52" s="5" t="n"/>
+      <c r="T52" s="11" t="n"/>
+      <c r="U52" s="5" t="n"/>
+      <c r="V52" s="5" t="n"/>
+      <c r="W52" s="5" t="n"/>
+      <c r="X52" s="5" t="n"/>
+    </row>
+    <row r="53" ht="6" customHeight="1"/>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>■ 문제점 · 건의사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="6" customHeight="1"/>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
+      <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="10" t="inlineStr">
+        <is>
+          <t>조치 방향</t>
+        </is>
+      </c>
+      <c r="S56" s="5" t="n"/>
+      <c r="T56" s="5" t="n"/>
+      <c r="U56" s="5" t="n"/>
+      <c r="V56" s="5" t="n"/>
+      <c r="W56" s="5" t="n"/>
+      <c r="X56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="11" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="12" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="5" t="n"/>
+      <c r="V57" s="5" t="n"/>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="11" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="12" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
+      <c r="U58" s="5" t="n"/>
+      <c r="V58" s="5" t="n"/>
+      <c r="W58" s="5" t="n"/>
+      <c r="X58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="11" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
+      <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="12" t="n"/>
+      <c r="S59" s="5" t="n"/>
+      <c r="T59" s="5" t="n"/>
+      <c r="U59" s="5" t="n"/>
+      <c r="V59" s="5" t="n"/>
+      <c r="W59" s="5" t="n"/>
+      <c r="X59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
+      <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="12" t="n"/>
+      <c r="S60" s="5" t="n"/>
+      <c r="T60" s="5" t="n"/>
+      <c r="U60" s="5" t="n"/>
+      <c r="V60" s="5" t="n"/>
+      <c r="W60" s="5" t="n"/>
+      <c r="X60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="11" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
+      <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="12" t="n"/>
+      <c r="S61" s="5" t="n"/>
+      <c r="T61" s="5" t="n"/>
+      <c r="U61" s="5" t="n"/>
+      <c r="V61" s="5" t="n"/>
+      <c r="W61" s="5" t="n"/>
+      <c r="X61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="6" customHeight="1"/>
+    <row r="63" ht="10" customHeight="1"/>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="14" t="inlineStr"/>
+      <c r="K65" s="15" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q65" s="16" t="n"/>
+      <c r="U65" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="14" t="inlineStr"/>
+      <c r="K66" s="15" t="inlineStr">
+        <is>
+          <t>감독(감리)</t>
+        </is>
+      </c>
+      <c r="Q66" s="16" t="n"/>
+      <c r="U66" s="17" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="6" customHeight="1"/>
+    <row r="69" ht="34" customHeight="1">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19.5" customHeight="1">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="178">
+    <mergeCell ref="E47:O47"/>
+    <mergeCell ref="A69:X69"/>
+    <mergeCell ref="N33:P33"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E61:Q61"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="R56:X56"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="E34:M34"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="R58:X58"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="E51:O51"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="E36:M36"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="R60:X60"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="N30:P30"/>
+    <mergeCell ref="U65:X65"/>
+    <mergeCell ref="P44:S44"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="R59:X59"/>
+    <mergeCell ref="K65:P65"/>
+    <mergeCell ref="E22:M22"/>
+    <mergeCell ref="E49:O49"/>
+    <mergeCell ref="P46:S46"/>
+    <mergeCell ref="E45:O45"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="G12:X12"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="Q35:T35"/>
+    <mergeCell ref="N32:P32"/>
+    <mergeCell ref="P48:S48"/>
+    <mergeCell ref="Q34:T34"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="Q36:T36"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="Q30:T30"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="P47:S47"/>
+    <mergeCell ref="Q17:T17"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="E48:O48"/>
+    <mergeCell ref="Q66:T66"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A42:X42"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="Q37:T37"/>
+    <mergeCell ref="N34:P34"/>
+    <mergeCell ref="P50:S50"/>
+    <mergeCell ref="E25:M25"/>
+    <mergeCell ref="R57:X57"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="N36:P36"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="P52:S52"/>
+    <mergeCell ref="E18:M18"/>
+    <mergeCell ref="Q29:T29"/>
+    <mergeCell ref="G8:X8"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="Q31:T31"/>
+    <mergeCell ref="G11:X11"/>
+    <mergeCell ref="A15:X15"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="E59:Q59"/>
+    <mergeCell ref="A64:X64"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="T46:X46"/>
+    <mergeCell ref="E20:M20"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="A70:X70"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="E29:M29"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="Q65:T65"/>
+    <mergeCell ref="E50:O50"/>
+    <mergeCell ref="T48:X48"/>
+    <mergeCell ref="A54:X54"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="G13:X13"/>
+    <mergeCell ref="E31:M31"/>
+    <mergeCell ref="T45:X45"/>
+    <mergeCell ref="E52:O52"/>
+    <mergeCell ref="A27:X27"/>
+    <mergeCell ref="T47:X47"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="R61:X61"/>
+    <mergeCell ref="T50:X50"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="T44:X44"/>
+    <mergeCell ref="P51:S51"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="E32:M32"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="T51:X51"/>
+    <mergeCell ref="N35:P35"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="P49:S49"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="E24:M24"/>
+    <mergeCell ref="N25:P25"/>
+    <mergeCell ref="E33:M33"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="T52:X52"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="E17:M17"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E35:M35"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="E19:M19"/>
+    <mergeCell ref="E57:Q57"/>
+    <mergeCell ref="T49:X49"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="Q32:T32"/>
+    <mergeCell ref="E30:M30"/>
+    <mergeCell ref="N29:P29"/>
+    <mergeCell ref="P45:S45"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="E44:O44"/>
+    <mergeCell ref="E56:Q56"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="E58:Q58"/>
+    <mergeCell ref="N31:P31"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="E37:M37"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="K66:P66"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="E46:O46"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="E21:M21"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="U66:X66"/>
+    <mergeCell ref="E60:Q60"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="E23:M23"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="Q22:T22"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>월 간  공 사 추 진  현 황  보 고 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공 사 명</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>가나지구 배수로 정비공사</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  발 주 기 관</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>가나시 건설과</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  계 약 금 액</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="7" t="n">
+        <v>963241000</v>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공        기</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2026. 3. 9. ~ 2026. 12. 31. (298일)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  작 성 일 자</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="8" t="n">
+        <v>46294</v>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="6" customHeight="1"/>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  보고 월</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>2026년 9월</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  공정률 (계획 / 실적)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>38.5% / 36.2%</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="5" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n"/>
+      <c r="W12" s="5" t="n"/>
+      <c r="X12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  기성률 (누계)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>57.94% (제3회)</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="5" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="5" t="n"/>
+      <c r="U13" s="5" t="n"/>
+      <c r="V13" s="5" t="n"/>
+      <c r="W13" s="5" t="n"/>
+      <c r="X13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>■ 당월 주요 시공 실적</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="6" customHeight="1"/>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>공종</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>시공 내용</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="5" t="n"/>
+      <c r="U17" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="5" t="n"/>
+      <c r="X17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>배수공</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>PE관 D600 부설</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>212m</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+      <c r="Q18" s="11" t="inlineStr">
+        <is>
+          <t>9. 1. ~ 9. 30.</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="5" t="n"/>
+      <c r="U18" s="11" t="inlineStr"/>
+      <c r="V18" s="5" t="n"/>
+      <c r="W18" s="5" t="n"/>
+      <c r="X18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>배수공</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>집수정 설치</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>6곳</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>9. 8. ~ 9. 26.</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="5" t="n"/>
+      <c r="U19" s="11" t="inlineStr"/>
+      <c r="V19" s="5" t="n"/>
+      <c r="W19" s="5" t="n"/>
+      <c r="X19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>구조물공</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>암거 A 상판·B 저판</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="11" t="inlineStr">
+        <is>
+          <t>V=96㎥</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="11" t="inlineStr">
+        <is>
+          <t>9. 10. ~ 9. 24.</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="11" t="inlineStr"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="11" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="11" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="11" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+      <c r="Q22" s="11" t="n"/>
+      <c r="R22" s="5" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="5" t="n"/>
+      <c r="U22" s="11" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="11" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="11" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="11" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="11" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="11" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="11" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="11" t="n"/>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>■ 익월 시공 계획</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>공종</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>시공 내용</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="10" t="inlineStr">
+        <is>
+          <t>수량</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="R29" s="5" t="n"/>
+      <c r="S29" s="5" t="n"/>
+      <c r="T29" s="5" t="n"/>
+      <c r="U29" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="V29" s="5" t="n"/>
+      <c r="W29" s="5" t="n"/>
+      <c r="X29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>배수공</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>PE관 D600 부설</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="11" t="inlineStr">
+        <is>
+          <t>250m</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+      <c r="Q30" s="11" t="inlineStr">
+        <is>
+          <t>10. 1. ~ 10. 31.</t>
+        </is>
+      </c>
+      <c r="R30" s="5" t="n"/>
+      <c r="S30" s="5" t="n"/>
+      <c r="T30" s="5" t="n"/>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>2개 조</t>
+        </is>
+      </c>
+      <c r="V30" s="5" t="n"/>
+      <c r="W30" s="5" t="n"/>
+      <c r="X30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>구조물공</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>암거 B 벽체·상판</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="11" t="inlineStr">
+        <is>
+          <t>V=102㎥</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>10. 5. ~ 10. 28.</t>
+        </is>
+      </c>
+      <c r="R31" s="5" t="n"/>
+      <c r="S31" s="5" t="n"/>
+      <c r="T31" s="5" t="n"/>
+      <c r="U31" s="11" t="inlineStr"/>
+      <c r="V31" s="5" t="n"/>
+      <c r="W31" s="5" t="n"/>
+      <c r="X31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="11" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="11" t="n"/>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="5" t="n"/>
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="11" t="n"/>
+      <c r="V32" s="5" t="n"/>
+      <c r="W32" s="5" t="n"/>
+      <c r="X32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+      <c r="Q33" s="11" t="n"/>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="5" t="n"/>
+      <c r="T33" s="5" t="n"/>
+      <c r="U33" s="11" t="n"/>
+      <c r="V33" s="5" t="n"/>
+      <c r="W33" s="5" t="n"/>
+      <c r="X33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="11" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+      <c r="Q34" s="11" t="n"/>
+      <c r="R34" s="5" t="n"/>
+      <c r="S34" s="5" t="n"/>
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="11" t="n"/>
+      <c r="V34" s="5" t="n"/>
+      <c r="W34" s="5" t="n"/>
+      <c r="X34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="11" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+      <c r="Q35" s="11" t="n"/>
+      <c r="R35" s="5" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="5" t="n"/>
+      <c r="U35" s="11" t="n"/>
+      <c r="V35" s="5" t="n"/>
+      <c r="W35" s="5" t="n"/>
+      <c r="X35" s="5" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="11" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
+      <c r="Q36" s="11" t="n"/>
+      <c r="R36" s="5" t="n"/>
+      <c r="S36" s="5" t="n"/>
+      <c r="T36" s="5" t="n"/>
+      <c r="U36" s="11" t="n"/>
+      <c r="V36" s="5" t="n"/>
+      <c r="W36" s="5" t="n"/>
+      <c r="X36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="11" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+      <c r="Q37" s="11" t="n"/>
+      <c r="R37" s="5" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="5" t="n"/>
+      <c r="U37" s="11" t="n"/>
+      <c r="V37" s="5" t="n"/>
+      <c r="W37" s="5" t="n"/>
+      <c r="X37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="6" customHeight="1"/>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>■ 인원·장비 / 안전·품질</t>
         </is>
@@ -1328,7 +2990,7 @@
     </row>
     <row r="40" ht="6" customHeight="1"/>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
@@ -1336,7 +2998,7 @@
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
       <c r="D41" s="5" t="n"/>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
@@ -1351,7 +3013,7 @@
       <c r="M41" s="5" t="n"/>
       <c r="N41" s="5" t="n"/>
       <c r="O41" s="5" t="n"/>
-      <c r="P41" s="8" t="inlineStr">
+      <c r="P41" s="10" t="inlineStr">
         <is>
           <t>수량·건수</t>
         </is>
@@ -1359,7 +3021,7 @@
       <c r="Q41" s="5" t="n"/>
       <c r="R41" s="5" t="n"/>
       <c r="S41" s="5" t="n"/>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="T41" s="10" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1370,11 +3032,19 @@
       <c r="X41" s="5" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="9" t="inlineStr"/>
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>인원</t>
+        </is>
+      </c>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
       <c r="D42" s="5" t="n"/>
-      <c r="E42" s="9" t="inlineStr"/>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>연인원(직영·협력)</t>
+        </is>
+      </c>
       <c r="F42" s="5" t="n"/>
       <c r="G42" s="5" t="n"/>
       <c r="H42" s="5" t="n"/>
@@ -1385,22 +3055,34 @@
       <c r="M42" s="5" t="n"/>
       <c r="N42" s="5" t="n"/>
       <c r="O42" s="5" t="n"/>
-      <c r="P42" s="9" t="inlineStr"/>
+      <c r="P42" s="11" t="inlineStr">
+        <is>
+          <t>612인</t>
+        </is>
+      </c>
       <c r="Q42" s="5" t="n"/>
       <c r="R42" s="5" t="n"/>
       <c r="S42" s="5" t="n"/>
-      <c r="T42" s="9" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr"/>
       <c r="U42" s="5" t="n"/>
       <c r="V42" s="5" t="n"/>
       <c r="W42" s="5" t="n"/>
       <c r="X42" s="5" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="9" t="inlineStr"/>
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
       <c r="D43" s="5" t="n"/>
-      <c r="E43" s="9" t="inlineStr"/>
+      <c r="E43" s="12" t="inlineStr">
+        <is>
+          <t>굴착기·덤프·크레인</t>
+        </is>
+      </c>
       <c r="F43" s="5" t="n"/>
       <c r="G43" s="5" t="n"/>
       <c r="H43" s="5" t="n"/>
@@ -1411,22 +3093,34 @@
       <c r="M43" s="5" t="n"/>
       <c r="N43" s="5" t="n"/>
       <c r="O43" s="5" t="n"/>
-      <c r="P43" s="9" t="inlineStr"/>
+      <c r="P43" s="11" t="inlineStr">
+        <is>
+          <t>148대</t>
+        </is>
+      </c>
       <c r="Q43" s="5" t="n"/>
       <c r="R43" s="5" t="n"/>
       <c r="S43" s="5" t="n"/>
-      <c r="T43" s="9" t="inlineStr"/>
+      <c r="T43" s="11" t="inlineStr"/>
       <c r="U43" s="5" t="n"/>
       <c r="V43" s="5" t="n"/>
       <c r="W43" s="5" t="n"/>
       <c r="X43" s="5" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="9" t="inlineStr"/>
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>안전</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="5" t="n"/>
       <c r="D44" s="5" t="n"/>
-      <c r="E44" s="9" t="inlineStr"/>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>TBM · 정기교육 · 위험성평가</t>
+        </is>
+      </c>
       <c r="F44" s="5" t="n"/>
       <c r="G44" s="5" t="n"/>
       <c r="H44" s="5" t="n"/>
@@ -1437,22 +3131,38 @@
       <c r="M44" s="5" t="n"/>
       <c r="N44" s="5" t="n"/>
       <c r="O44" s="5" t="n"/>
-      <c r="P44" s="9" t="inlineStr"/>
+      <c r="P44" s="11" t="inlineStr">
+        <is>
+          <t>30회</t>
+        </is>
+      </c>
       <c r="Q44" s="5" t="n"/>
       <c r="R44" s="5" t="n"/>
       <c r="S44" s="5" t="n"/>
-      <c r="T44" s="9" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr">
+        <is>
+          <t>무재해</t>
+        </is>
+      </c>
       <c r="U44" s="5" t="n"/>
       <c r="V44" s="5" t="n"/>
       <c r="W44" s="5" t="n"/>
       <c r="X44" s="5" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="9" t="inlineStr"/>
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>품질</t>
+        </is>
+      </c>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="5" t="n"/>
-      <c r="E45" s="9" t="inlineStr"/>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>레미콘 반입 검사 · 강도 시험</t>
+        </is>
+      </c>
       <c r="F45" s="5" t="n"/>
       <c r="G45" s="5" t="n"/>
       <c r="H45" s="5" t="n"/>
@@ -1463,22 +3173,30 @@
       <c r="M45" s="5" t="n"/>
       <c r="N45" s="5" t="n"/>
       <c r="O45" s="5" t="n"/>
-      <c r="P45" s="9" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr">
+        <is>
+          <t>12회</t>
+        </is>
+      </c>
       <c r="Q45" s="5" t="n"/>
       <c r="R45" s="5" t="n"/>
       <c r="S45" s="5" t="n"/>
-      <c r="T45" s="9" t="inlineStr"/>
+      <c r="T45" s="11" t="inlineStr">
+        <is>
+          <t>반품 1대</t>
+        </is>
+      </c>
       <c r="U45" s="5" t="n"/>
       <c r="V45" s="5" t="n"/>
       <c r="W45" s="5" t="n"/>
       <c r="X45" s="5" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="9" t="inlineStr"/>
+      <c r="A46" s="11" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="5" t="n"/>
       <c r="D46" s="5" t="n"/>
-      <c r="E46" s="9" t="inlineStr"/>
+      <c r="E46" s="12" t="n"/>
       <c r="F46" s="5" t="n"/>
       <c r="G46" s="5" t="n"/>
       <c r="H46" s="5" t="n"/>
@@ -1489,22 +3207,22 @@
       <c r="M46" s="5" t="n"/>
       <c r="N46" s="5" t="n"/>
       <c r="O46" s="5" t="n"/>
-      <c r="P46" s="9" t="inlineStr"/>
+      <c r="P46" s="11" t="n"/>
       <c r="Q46" s="5" t="n"/>
       <c r="R46" s="5" t="n"/>
       <c r="S46" s="5" t="n"/>
-      <c r="T46" s="9" t="inlineStr"/>
+      <c r="T46" s="11" t="n"/>
       <c r="U46" s="5" t="n"/>
       <c r="V46" s="5" t="n"/>
       <c r="W46" s="5" t="n"/>
       <c r="X46" s="5" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="9" t="inlineStr"/>
+      <c r="A47" s="11" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="5" t="n"/>
       <c r="D47" s="5" t="n"/>
-      <c r="E47" s="9" t="inlineStr"/>
+      <c r="E47" s="12" t="n"/>
       <c r="F47" s="5" t="n"/>
       <c r="G47" s="5" t="n"/>
       <c r="H47" s="5" t="n"/>
@@ -1515,22 +3233,22 @@
       <c r="M47" s="5" t="n"/>
       <c r="N47" s="5" t="n"/>
       <c r="O47" s="5" t="n"/>
-      <c r="P47" s="9" t="inlineStr"/>
+      <c r="P47" s="11" t="n"/>
       <c r="Q47" s="5" t="n"/>
       <c r="R47" s="5" t="n"/>
       <c r="S47" s="5" t="n"/>
-      <c r="T47" s="9" t="inlineStr"/>
+      <c r="T47" s="11" t="n"/>
       <c r="U47" s="5" t="n"/>
       <c r="V47" s="5" t="n"/>
       <c r="W47" s="5" t="n"/>
       <c r="X47" s="5" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="9" t="inlineStr"/>
+      <c r="A48" s="11" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="5" t="n"/>
-      <c r="E48" s="9" t="inlineStr"/>
+      <c r="E48" s="12" t="n"/>
       <c r="F48" s="5" t="n"/>
       <c r="G48" s="5" t="n"/>
       <c r="H48" s="5" t="n"/>
@@ -1541,22 +3259,22 @@
       <c r="M48" s="5" t="n"/>
       <c r="N48" s="5" t="n"/>
       <c r="O48" s="5" t="n"/>
-      <c r="P48" s="9" t="inlineStr"/>
+      <c r="P48" s="11" t="n"/>
       <c r="Q48" s="5" t="n"/>
       <c r="R48" s="5" t="n"/>
       <c r="S48" s="5" t="n"/>
-      <c r="T48" s="9" t="inlineStr"/>
+      <c r="T48" s="11" t="n"/>
       <c r="U48" s="5" t="n"/>
       <c r="V48" s="5" t="n"/>
       <c r="W48" s="5" t="n"/>
       <c r="X48" s="5" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="9" t="inlineStr"/>
+      <c r="A49" s="11" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
       <c r="D49" s="5" t="n"/>
-      <c r="E49" s="9" t="inlineStr"/>
+      <c r="E49" s="12" t="n"/>
       <c r="F49" s="5" t="n"/>
       <c r="G49" s="5" t="n"/>
       <c r="H49" s="5" t="n"/>
@@ -1567,11 +3285,11 @@
       <c r="M49" s="5" t="n"/>
       <c r="N49" s="5" t="n"/>
       <c r="O49" s="5" t="n"/>
-      <c r="P49" s="9" t="inlineStr"/>
+      <c r="P49" s="11" t="n"/>
       <c r="Q49" s="5" t="n"/>
       <c r="R49" s="5" t="n"/>
       <c r="S49" s="5" t="n"/>
-      <c r="T49" s="9" t="inlineStr"/>
+      <c r="T49" s="11" t="n"/>
       <c r="U49" s="5" t="n"/>
       <c r="V49" s="5" t="n"/>
       <c r="W49" s="5" t="n"/>
@@ -1579,7 +3297,7 @@
     </row>
     <row r="50" ht="6" customHeight="1"/>
     <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>■ 문제점 · 건의사항</t>
         </is>
@@ -1587,7 +3305,7 @@
     </row>
     <row r="52" ht="6" customHeight="1"/>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>구분</t>
         </is>
@@ -1595,7 +3313,7 @@
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="5" t="n"/>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
@@ -1612,7 +3330,7 @@
       <c r="O53" s="5" t="n"/>
       <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="8" t="inlineStr">
+      <c r="R53" s="10" t="inlineStr">
         <is>
           <t>조치 방향</t>
         </is>
@@ -1625,11 +3343,19 @@
       <c r="X53" s="5" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="9" t="inlineStr"/>
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>공정</t>
+        </is>
+      </c>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="5" t="n"/>
       <c r="D54" s="5" t="n"/>
-      <c r="E54" s="9" t="inlineStr"/>
+      <c r="E54" s="12" t="inlineStr">
+        <is>
+          <t>7월 호우로 배수공 2.3%p 지연</t>
+        </is>
+      </c>
       <c r="F54" s="5" t="n"/>
       <c r="G54" s="5" t="n"/>
       <c r="H54" s="5" t="n"/>
@@ -1642,7 +3368,11 @@
       <c r="O54" s="5" t="n"/>
       <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="9" t="inlineStr"/>
+      <c r="R54" s="12" t="inlineStr">
+        <is>
+          <t>10월 2개 조 투입으로 만회</t>
+        </is>
+      </c>
       <c r="S54" s="5" t="n"/>
       <c r="T54" s="5" t="n"/>
       <c r="U54" s="5" t="n"/>
@@ -1651,11 +3381,19 @@
       <c r="X54" s="5" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="9" t="inlineStr"/>
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="5" t="n"/>
       <c r="D55" s="5" t="n"/>
-      <c r="E55" s="9" t="inlineStr"/>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>관급 맨홀뚜껑 반입 일정 미정</t>
+        </is>
+      </c>
       <c r="F55" s="5" t="n"/>
       <c r="G55" s="5" t="n"/>
       <c r="H55" s="5" t="n"/>
@@ -1668,7 +3406,11 @@
       <c r="O55" s="5" t="n"/>
       <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="n"/>
-      <c r="R55" s="9" t="inlineStr"/>
+      <c r="R55" s="12" t="inlineStr">
+        <is>
+          <t>발주기관에 일정 확인 요청</t>
+        </is>
+      </c>
       <c r="S55" s="5" t="n"/>
       <c r="T55" s="5" t="n"/>
       <c r="U55" s="5" t="n"/>
@@ -1677,11 +3419,11 @@
       <c r="X55" s="5" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="9" t="inlineStr"/>
+      <c r="A56" s="11" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="5" t="n"/>
       <c r="D56" s="5" t="n"/>
-      <c r="E56" s="9" t="inlineStr"/>
+      <c r="E56" s="12" t="n"/>
       <c r="F56" s="5" t="n"/>
       <c r="G56" s="5" t="n"/>
       <c r="H56" s="5" t="n"/>
@@ -1694,7 +3436,7 @@
       <c r="O56" s="5" t="n"/>
       <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="9" t="inlineStr"/>
+      <c r="R56" s="12" t="n"/>
       <c r="S56" s="5" t="n"/>
       <c r="T56" s="5" t="n"/>
       <c r="U56" s="5" t="n"/>
@@ -1703,11 +3445,11 @@
       <c r="X56" s="5" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="9" t="inlineStr"/>
+      <c r="A57" s="11" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="5" t="n"/>
       <c r="D57" s="5" t="n"/>
-      <c r="E57" s="9" t="inlineStr"/>
+      <c r="E57" s="12" t="n"/>
       <c r="F57" s="5" t="n"/>
       <c r="G57" s="5" t="n"/>
       <c r="H57" s="5" t="n"/>
@@ -1720,7 +3462,7 @@
       <c r="O57" s="5" t="n"/>
       <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="9" t="inlineStr"/>
+      <c r="R57" s="12" t="n"/>
       <c r="S57" s="5" t="n"/>
       <c r="T57" s="5" t="n"/>
       <c r="U57" s="5" t="n"/>
@@ -1729,11 +3471,11 @@
       <c r="X57" s="5" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="9" t="inlineStr"/>
+      <c r="A58" s="11" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="5" t="n"/>
       <c r="D58" s="5" t="n"/>
-      <c r="E58" s="9" t="inlineStr"/>
+      <c r="E58" s="12" t="n"/>
       <c r="F58" s="5" t="n"/>
       <c r="G58" s="5" t="n"/>
       <c r="H58" s="5" t="n"/>
@@ -1746,7 +3488,7 @@
       <c r="O58" s="5" t="n"/>
       <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="9" t="inlineStr"/>
+      <c r="R58" s="12" t="n"/>
       <c r="S58" s="5" t="n"/>
       <c r="T58" s="5" t="n"/>
       <c r="U58" s="5" t="n"/>
@@ -1757,46 +3499,56 @@
     <row r="59" ht="6" customHeight="1"/>
     <row r="60" ht="10" customHeight="1"/>
     <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="K62" s="11" t="inlineStr">
+      <c r="A61" s="13" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="14" t="inlineStr"/>
+      <c r="K62" s="15" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="Q62" s="16" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U62" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="K63" s="11" t="inlineStr">
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="14" t="inlineStr"/>
+      <c r="K63" s="15" t="inlineStr">
         <is>
           <t>감독(감리)</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
+      <c r="Q63" s="16" t="inlineStr">
+        <is>
+          <t>박감리</t>
+        </is>
+      </c>
+      <c r="U63" s="17" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="64" ht="6" customHeight="1"/>
-    <row r="67">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="66" ht="19.5" customHeight="1">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="173">
+  <mergeCells count="177">
     <mergeCell ref="E47:O47"/>
     <mergeCell ref="N33:P33"/>
     <mergeCell ref="A20:D20"/>
@@ -1809,6 +3561,7 @@
     <mergeCell ref="P42:S42"/>
     <mergeCell ref="E54:Q54"/>
     <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A63:J63"/>
     <mergeCell ref="A3:X3"/>
     <mergeCell ref="R58:X58"/>
     <mergeCell ref="A31:D31"/>
@@ -1819,26 +3572,26 @@
     <mergeCell ref="E36:M36"/>
     <mergeCell ref="Q21:T21"/>
     <mergeCell ref="A24:D24"/>
+    <mergeCell ref="Q62:T62"/>
     <mergeCell ref="N30:P30"/>
     <mergeCell ref="P44:S44"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="E22:M22"/>
     <mergeCell ref="A54:D54"/>
+    <mergeCell ref="K62:P62"/>
     <mergeCell ref="E49:O49"/>
     <mergeCell ref="A41:D41"/>
     <mergeCell ref="P46:S46"/>
     <mergeCell ref="E45:O45"/>
     <mergeCell ref="U25:X25"/>
-    <mergeCell ref="A67:X67"/>
+    <mergeCell ref="Q63:T63"/>
     <mergeCell ref="G12:X12"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="Q35:T35"/>
     <mergeCell ref="N32:P32"/>
-    <mergeCell ref="S62:X62"/>
     <mergeCell ref="P48:S48"/>
     <mergeCell ref="Q34:T34"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="K62:R62"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A17:D17"/>
@@ -1854,6 +3607,7 @@
     <mergeCell ref="P43:S43"/>
     <mergeCell ref="A19:D19"/>
     <mergeCell ref="U20:X20"/>
+    <mergeCell ref="A66:X66"/>
     <mergeCell ref="E48:O48"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="U22:X22"/>
@@ -1887,9 +3641,11 @@
     <mergeCell ref="U18:X18"/>
     <mergeCell ref="E29:M29"/>
     <mergeCell ref="U33:X33"/>
+    <mergeCell ref="K63:P63"/>
     <mergeCell ref="R54:X54"/>
     <mergeCell ref="T48:X48"/>
     <mergeCell ref="R53:X53"/>
+    <mergeCell ref="A62:J62"/>
     <mergeCell ref="N23:P23"/>
     <mergeCell ref="G13:X13"/>
     <mergeCell ref="E31:M31"/>
@@ -1902,7 +3658,6 @@
     <mergeCell ref="E53:Q53"/>
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="T44:X44"/>
-    <mergeCell ref="K63:R63"/>
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="A36:D36"/>
     <mergeCell ref="E55:Q55"/>
@@ -1928,6 +3683,7 @@
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="E35:M35"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="U62:X62"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="E43:O43"/>
     <mergeCell ref="E19:M19"/>
@@ -1940,6 +3696,7 @@
     <mergeCell ref="Q32:T32"/>
     <mergeCell ref="E30:M30"/>
     <mergeCell ref="N29:P29"/>
+    <mergeCell ref="U63:X63"/>
     <mergeCell ref="P45:S45"/>
     <mergeCell ref="U35:X35"/>
     <mergeCell ref="E44:O44"/>
@@ -1955,7 +3712,6 @@
     <mergeCell ref="N24:P24"/>
     <mergeCell ref="E37:M37"/>
     <mergeCell ref="U30:X30"/>
-    <mergeCell ref="S63:X63"/>
     <mergeCell ref="U17:X17"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="E46:O46"/>
@@ -1971,7 +3727,8 @@
     <mergeCell ref="A47:D47"/>
     <mergeCell ref="Q22:T22"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/wolgan-bogoseo.xlsx
+++ b/web/public/forms/wolgan-bogoseo.xlsx
@@ -581,7 +581,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="19" t="inlineStr">

--- a/web/public/forms/wolgan-bogoseo.xlsx
+++ b/web/public/forms/wolgan-bogoseo.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월간 공사추진현황 보고서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'월간 공사추진현황 보고서'!$A$1:$X$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -180,9 +178,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1843,6 +1838,7 @@
       </c>
     </row>
     <row r="67" ht="6" customHeight="1"/>
+    <row r="68"/>
     <row r="69" ht="34" customHeight="1">
       <c r="A69" s="18" t="inlineStr">
         <is>
@@ -2042,1693 +2038,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X66"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>월 간  공 사 추 진  현 황  보 고 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공 사 명</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>가나지구 배수로 정비공사</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  발 주 기 관</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>가나시 건설과</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  계 약 금 액</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="7" t="n">
-        <v>963241000</v>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공        기</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>2026. 3. 9. ~ 2026. 12. 31. (298일)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  작 성 일 자</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="8" t="n">
-        <v>46294</v>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="6" customHeight="1"/>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  보고 월</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2026년 9월</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  공정률 (계획 / 실적)</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>38.5% / 36.2%</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
-      <c r="I12" s="5" t="n"/>
-      <c r="J12" s="5" t="n"/>
-      <c r="K12" s="5" t="n"/>
-      <c r="L12" s="5" t="n"/>
-      <c r="M12" s="5" t="n"/>
-      <c r="N12" s="5" t="n"/>
-      <c r="O12" s="5" t="n"/>
-      <c r="P12" s="5" t="n"/>
-      <c r="Q12" s="5" t="n"/>
-      <c r="R12" s="5" t="n"/>
-      <c r="S12" s="5" t="n"/>
-      <c r="T12" s="5" t="n"/>
-      <c r="U12" s="5" t="n"/>
-      <c r="V12" s="5" t="n"/>
-      <c r="W12" s="5" t="n"/>
-      <c r="X12" s="5" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  기성률 (누계)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>57.94% (제3회)</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
-      <c r="K13" s="5" t="n"/>
-      <c r="L13" s="5" t="n"/>
-      <c r="M13" s="5" t="n"/>
-      <c r="N13" s="5" t="n"/>
-      <c r="O13" s="5" t="n"/>
-      <c r="P13" s="5" t="n"/>
-      <c r="Q13" s="5" t="n"/>
-      <c r="R13" s="5" t="n"/>
-      <c r="S13" s="5" t="n"/>
-      <c r="T13" s="5" t="n"/>
-      <c r="U13" s="5" t="n"/>
-      <c r="V13" s="5" t="n"/>
-      <c r="W13" s="5" t="n"/>
-      <c r="X13" s="5" t="n"/>
-    </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>■ 당월 주요 시공 실적</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="6" customHeight="1"/>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>공종</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="10" t="inlineStr">
-        <is>
-          <t>시공 내용</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="5" t="n"/>
-      <c r="J17" s="5" t="n"/>
-      <c r="K17" s="5" t="n"/>
-      <c r="L17" s="5" t="n"/>
-      <c r="M17" s="5" t="n"/>
-      <c r="N17" s="10" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="n"/>
-      <c r="P17" s="5" t="n"/>
-      <c r="Q17" s="10" t="inlineStr">
-        <is>
-          <t>기간</t>
-        </is>
-      </c>
-      <c r="R17" s="5" t="n"/>
-      <c r="S17" s="5" t="n"/>
-      <c r="T17" s="5" t="n"/>
-      <c r="U17" s="10" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="V17" s="5" t="n"/>
-      <c r="W17" s="5" t="n"/>
-      <c r="X17" s="5" t="n"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>배수공</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="12" t="inlineStr">
-        <is>
-          <t>PE관 D600 부설</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-      <c r="I18" s="5" t="n"/>
-      <c r="J18" s="5" t="n"/>
-      <c r="K18" s="5" t="n"/>
-      <c r="L18" s="5" t="n"/>
-      <c r="M18" s="5" t="n"/>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>212m</t>
-        </is>
-      </c>
-      <c r="O18" s="5" t="n"/>
-      <c r="P18" s="5" t="n"/>
-      <c r="Q18" s="11" t="inlineStr">
-        <is>
-          <t>9. 1. ~ 9. 30.</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="n"/>
-      <c r="S18" s="5" t="n"/>
-      <c r="T18" s="5" t="n"/>
-      <c r="U18" s="11" t="inlineStr"/>
-      <c r="V18" s="5" t="n"/>
-      <c r="W18" s="5" t="n"/>
-      <c r="X18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>배수공</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>집수정 설치</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-      <c r="I19" s="5" t="n"/>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-      <c r="M19" s="5" t="n"/>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>6곳</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="n"/>
-      <c r="P19" s="5" t="n"/>
-      <c r="Q19" s="11" t="inlineStr">
-        <is>
-          <t>9. 8. ~ 9. 26.</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="n"/>
-      <c r="S19" s="5" t="n"/>
-      <c r="T19" s="5" t="n"/>
-      <c r="U19" s="11" t="inlineStr"/>
-      <c r="V19" s="5" t="n"/>
-      <c r="W19" s="5" t="n"/>
-      <c r="X19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>구조물공</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="12" t="inlineStr">
-        <is>
-          <t>암거 A 상판·B 저판</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-      <c r="M20" s="5" t="n"/>
-      <c r="N20" s="11" t="inlineStr">
-        <is>
-          <t>V=96㎥</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="n"/>
-      <c r="P20" s="5" t="n"/>
-      <c r="Q20" s="11" t="inlineStr">
-        <is>
-          <t>9. 10. ~ 9. 24.</t>
-        </is>
-      </c>
-      <c r="R20" s="5" t="n"/>
-      <c r="S20" s="5" t="n"/>
-      <c r="T20" s="5" t="n"/>
-      <c r="U20" s="11" t="inlineStr"/>
-      <c r="V20" s="5" t="n"/>
-      <c r="W20" s="5" t="n"/>
-      <c r="X20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-      <c r="I21" s="5" t="n"/>
-      <c r="J21" s="5" t="n"/>
-      <c r="K21" s="5" t="n"/>
-      <c r="L21" s="5" t="n"/>
-      <c r="M21" s="5" t="n"/>
-      <c r="N21" s="11" t="n"/>
-      <c r="O21" s="5" t="n"/>
-      <c r="P21" s="5" t="n"/>
-      <c r="Q21" s="11" t="n"/>
-      <c r="R21" s="5" t="n"/>
-      <c r="S21" s="5" t="n"/>
-      <c r="T21" s="5" t="n"/>
-      <c r="U21" s="11" t="n"/>
-      <c r="V21" s="5" t="n"/>
-      <c r="W21" s="5" t="n"/>
-      <c r="X21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-      <c r="I22" s="5" t="n"/>
-      <c r="J22" s="5" t="n"/>
-      <c r="K22" s="5" t="n"/>
-      <c r="L22" s="5" t="n"/>
-      <c r="M22" s="5" t="n"/>
-      <c r="N22" s="11" t="n"/>
-      <c r="O22" s="5" t="n"/>
-      <c r="P22" s="5" t="n"/>
-      <c r="Q22" s="11" t="n"/>
-      <c r="R22" s="5" t="n"/>
-      <c r="S22" s="5" t="n"/>
-      <c r="T22" s="5" t="n"/>
-      <c r="U22" s="11" t="n"/>
-      <c r="V22" s="5" t="n"/>
-      <c r="W22" s="5" t="n"/>
-      <c r="X22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="11" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="11" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="11" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="11" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="11" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="11" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="11" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="11" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="11" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="6" customHeight="1"/>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>■ 익월 시공 계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>공종</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>시공 내용</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="5" t="n"/>
-      <c r="I29" s="5" t="n"/>
-      <c r="J29" s="5" t="n"/>
-      <c r="K29" s="5" t="n"/>
-      <c r="L29" s="5" t="n"/>
-      <c r="M29" s="5" t="n"/>
-      <c r="N29" s="10" t="inlineStr">
-        <is>
-          <t>수량</t>
-        </is>
-      </c>
-      <c r="O29" s="5" t="n"/>
-      <c r="P29" s="5" t="n"/>
-      <c r="Q29" s="10" t="inlineStr">
-        <is>
-          <t>기간</t>
-        </is>
-      </c>
-      <c r="R29" s="5" t="n"/>
-      <c r="S29" s="5" t="n"/>
-      <c r="T29" s="5" t="n"/>
-      <c r="U29" s="10" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="V29" s="5" t="n"/>
-      <c r="W29" s="5" t="n"/>
-      <c r="X29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>배수공</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>PE관 D600 부설</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="5" t="n"/>
-      <c r="I30" s="5" t="n"/>
-      <c r="J30" s="5" t="n"/>
-      <c r="K30" s="5" t="n"/>
-      <c r="L30" s="5" t="n"/>
-      <c r="M30" s="5" t="n"/>
-      <c r="N30" s="11" t="inlineStr">
-        <is>
-          <t>250m</t>
-        </is>
-      </c>
-      <c r="O30" s="5" t="n"/>
-      <c r="P30" s="5" t="n"/>
-      <c r="Q30" s="11" t="inlineStr">
-        <is>
-          <t>10. 1. ~ 10. 31.</t>
-        </is>
-      </c>
-      <c r="R30" s="5" t="n"/>
-      <c r="S30" s="5" t="n"/>
-      <c r="T30" s="5" t="n"/>
-      <c r="U30" s="11" t="inlineStr">
-        <is>
-          <t>2개 조</t>
-        </is>
-      </c>
-      <c r="V30" s="5" t="n"/>
-      <c r="W30" s="5" t="n"/>
-      <c r="X30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>구조물공</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>암거 B 벽체·상판</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="5" t="n"/>
-      <c r="I31" s="5" t="n"/>
-      <c r="J31" s="5" t="n"/>
-      <c r="K31" s="5" t="n"/>
-      <c r="L31" s="5" t="n"/>
-      <c r="M31" s="5" t="n"/>
-      <c r="N31" s="11" t="inlineStr">
-        <is>
-          <t>V=102㎥</t>
-        </is>
-      </c>
-      <c r="O31" s="5" t="n"/>
-      <c r="P31" s="5" t="n"/>
-      <c r="Q31" s="11" t="inlineStr">
-        <is>
-          <t>10. 5. ~ 10. 28.</t>
-        </is>
-      </c>
-      <c r="R31" s="5" t="n"/>
-      <c r="S31" s="5" t="n"/>
-      <c r="T31" s="5" t="n"/>
-      <c r="U31" s="11" t="inlineStr"/>
-      <c r="V31" s="5" t="n"/>
-      <c r="W31" s="5" t="n"/>
-      <c r="X31" s="5" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
-      <c r="H32" s="5" t="n"/>
-      <c r="I32" s="5" t="n"/>
-      <c r="J32" s="5" t="n"/>
-      <c r="K32" s="5" t="n"/>
-      <c r="L32" s="5" t="n"/>
-      <c r="M32" s="5" t="n"/>
-      <c r="N32" s="11" t="n"/>
-      <c r="O32" s="5" t="n"/>
-      <c r="P32" s="5" t="n"/>
-      <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="5" t="n"/>
-      <c r="S32" s="5" t="n"/>
-      <c r="T32" s="5" t="n"/>
-      <c r="U32" s="11" t="n"/>
-      <c r="V32" s="5" t="n"/>
-      <c r="W32" s="5" t="n"/>
-      <c r="X32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
-      <c r="K33" s="5" t="n"/>
-      <c r="L33" s="5" t="n"/>
-      <c r="M33" s="5" t="n"/>
-      <c r="N33" s="11" t="n"/>
-      <c r="O33" s="5" t="n"/>
-      <c r="P33" s="5" t="n"/>
-      <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="5" t="n"/>
-      <c r="S33" s="5" t="n"/>
-      <c r="T33" s="5" t="n"/>
-      <c r="U33" s="11" t="n"/>
-      <c r="V33" s="5" t="n"/>
-      <c r="W33" s="5" t="n"/>
-      <c r="X33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
-      <c r="H34" s="5" t="n"/>
-      <c r="I34" s="5" t="n"/>
-      <c r="J34" s="5" t="n"/>
-      <c r="K34" s="5" t="n"/>
-      <c r="L34" s="5" t="n"/>
-      <c r="M34" s="5" t="n"/>
-      <c r="N34" s="11" t="n"/>
-      <c r="O34" s="5" t="n"/>
-      <c r="P34" s="5" t="n"/>
-      <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="5" t="n"/>
-      <c r="S34" s="5" t="n"/>
-      <c r="T34" s="5" t="n"/>
-      <c r="U34" s="11" t="n"/>
-      <c r="V34" s="5" t="n"/>
-      <c r="W34" s="5" t="n"/>
-      <c r="X34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
-      <c r="H35" s="5" t="n"/>
-      <c r="I35" s="5" t="n"/>
-      <c r="J35" s="5" t="n"/>
-      <c r="K35" s="5" t="n"/>
-      <c r="L35" s="5" t="n"/>
-      <c r="M35" s="5" t="n"/>
-      <c r="N35" s="11" t="n"/>
-      <c r="O35" s="5" t="n"/>
-      <c r="P35" s="5" t="n"/>
-      <c r="Q35" s="11" t="n"/>
-      <c r="R35" s="5" t="n"/>
-      <c r="S35" s="5" t="n"/>
-      <c r="T35" s="5" t="n"/>
-      <c r="U35" s="11" t="n"/>
-      <c r="V35" s="5" t="n"/>
-      <c r="W35" s="5" t="n"/>
-      <c r="X35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="11" t="n"/>
-      <c r="B36" s="5" t="n"/>
-      <c r="C36" s="5" t="n"/>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
-      <c r="H36" s="5" t="n"/>
-      <c r="I36" s="5" t="n"/>
-      <c r="J36" s="5" t="n"/>
-      <c r="K36" s="5" t="n"/>
-      <c r="L36" s="5" t="n"/>
-      <c r="M36" s="5" t="n"/>
-      <c r="N36" s="11" t="n"/>
-      <c r="O36" s="5" t="n"/>
-      <c r="P36" s="5" t="n"/>
-      <c r="Q36" s="11" t="n"/>
-      <c r="R36" s="5" t="n"/>
-      <c r="S36" s="5" t="n"/>
-      <c r="T36" s="5" t="n"/>
-      <c r="U36" s="11" t="n"/>
-      <c r="V36" s="5" t="n"/>
-      <c r="W36" s="5" t="n"/>
-      <c r="X36" s="5" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
-      <c r="H37" s="5" t="n"/>
-      <c r="I37" s="5" t="n"/>
-      <c r="J37" s="5" t="n"/>
-      <c r="K37" s="5" t="n"/>
-      <c r="L37" s="5" t="n"/>
-      <c r="M37" s="5" t="n"/>
-      <c r="N37" s="11" t="n"/>
-      <c r="O37" s="5" t="n"/>
-      <c r="P37" s="5" t="n"/>
-      <c r="Q37" s="11" t="n"/>
-      <c r="R37" s="5" t="n"/>
-      <c r="S37" s="5" t="n"/>
-      <c r="T37" s="5" t="n"/>
-      <c r="U37" s="11" t="n"/>
-      <c r="V37" s="5" t="n"/>
-      <c r="W37" s="5" t="n"/>
-      <c r="X37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="6" customHeight="1"/>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>■ 인원·장비 / 안전·품질</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="6" customHeight="1"/>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="n"/>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="10" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
-      <c r="H41" s="5" t="n"/>
-      <c r="I41" s="5" t="n"/>
-      <c r="J41" s="5" t="n"/>
-      <c r="K41" s="5" t="n"/>
-      <c r="L41" s="5" t="n"/>
-      <c r="M41" s="5" t="n"/>
-      <c r="N41" s="5" t="n"/>
-      <c r="O41" s="5" t="n"/>
-      <c r="P41" s="10" t="inlineStr">
-        <is>
-          <t>수량·건수</t>
-        </is>
-      </c>
-      <c r="Q41" s="5" t="n"/>
-      <c r="R41" s="5" t="n"/>
-      <c r="S41" s="5" t="n"/>
-      <c r="T41" s="10" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="U41" s="5" t="n"/>
-      <c r="V41" s="5" t="n"/>
-      <c r="W41" s="5" t="n"/>
-      <c r="X41" s="5" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="11" t="inlineStr">
-        <is>
-          <t>인원</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>연인원(직영·협력)</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
-      <c r="K42" s="5" t="n"/>
-      <c r="L42" s="5" t="n"/>
-      <c r="M42" s="5" t="n"/>
-      <c r="N42" s="5" t="n"/>
-      <c r="O42" s="5" t="n"/>
-      <c r="P42" s="11" t="inlineStr">
-        <is>
-          <t>612인</t>
-        </is>
-      </c>
-      <c r="Q42" s="5" t="n"/>
-      <c r="R42" s="5" t="n"/>
-      <c r="S42" s="5" t="n"/>
-      <c r="T42" s="11" t="inlineStr"/>
-      <c r="U42" s="5" t="n"/>
-      <c r="V42" s="5" t="n"/>
-      <c r="W42" s="5" t="n"/>
-      <c r="X42" s="5" t="n"/>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>장비</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="n"/>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>굴착기·덤프·크레인</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-      <c r="L43" s="5" t="n"/>
-      <c r="M43" s="5" t="n"/>
-      <c r="N43" s="5" t="n"/>
-      <c r="O43" s="5" t="n"/>
-      <c r="P43" s="11" t="inlineStr">
-        <is>
-          <t>148대</t>
-        </is>
-      </c>
-      <c r="Q43" s="5" t="n"/>
-      <c r="R43" s="5" t="n"/>
-      <c r="S43" s="5" t="n"/>
-      <c r="T43" s="11" t="inlineStr"/>
-      <c r="U43" s="5" t="n"/>
-      <c r="V43" s="5" t="n"/>
-      <c r="W43" s="5" t="n"/>
-      <c r="X43" s="5" t="n"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>안전</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="n"/>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>TBM · 정기교육 · 위험성평가</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-      <c r="L44" s="5" t="n"/>
-      <c r="M44" s="5" t="n"/>
-      <c r="N44" s="5" t="n"/>
-      <c r="O44" s="5" t="n"/>
-      <c r="P44" s="11" t="inlineStr">
-        <is>
-          <t>30회</t>
-        </is>
-      </c>
-      <c r="Q44" s="5" t="n"/>
-      <c r="R44" s="5" t="n"/>
-      <c r="S44" s="5" t="n"/>
-      <c r="T44" s="11" t="inlineStr">
-        <is>
-          <t>무재해</t>
-        </is>
-      </c>
-      <c r="U44" s="5" t="n"/>
-      <c r="V44" s="5" t="n"/>
-      <c r="W44" s="5" t="n"/>
-      <c r="X44" s="5" t="n"/>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
-        <is>
-          <t>품질</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="n"/>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>레미콘 반입 검사 · 강도 시험</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-      <c r="L45" s="5" t="n"/>
-      <c r="M45" s="5" t="n"/>
-      <c r="N45" s="5" t="n"/>
-      <c r="O45" s="5" t="n"/>
-      <c r="P45" s="11" t="inlineStr">
-        <is>
-          <t>12회</t>
-        </is>
-      </c>
-      <c r="Q45" s="5" t="n"/>
-      <c r="R45" s="5" t="n"/>
-      <c r="S45" s="5" t="n"/>
-      <c r="T45" s="11" t="inlineStr">
-        <is>
-          <t>반품 1대</t>
-        </is>
-      </c>
-      <c r="U45" s="5" t="n"/>
-      <c r="V45" s="5" t="n"/>
-      <c r="W45" s="5" t="n"/>
-      <c r="X45" s="5" t="n"/>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="11" t="n"/>
-      <c r="B46" s="5" t="n"/>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-      <c r="L46" s="5" t="n"/>
-      <c r="M46" s="5" t="n"/>
-      <c r="N46" s="5" t="n"/>
-      <c r="O46" s="5" t="n"/>
-      <c r="P46" s="11" t="n"/>
-      <c r="Q46" s="5" t="n"/>
-      <c r="R46" s="5" t="n"/>
-      <c r="S46" s="5" t="n"/>
-      <c r="T46" s="11" t="n"/>
-      <c r="U46" s="5" t="n"/>
-      <c r="V46" s="5" t="n"/>
-      <c r="W46" s="5" t="n"/>
-      <c r="X46" s="5" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="11" t="n"/>
-      <c r="B47" s="5" t="n"/>
-      <c r="C47" s="5" t="n"/>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
-      <c r="H47" s="5" t="n"/>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="5" t="n"/>
-      <c r="K47" s="5" t="n"/>
-      <c r="L47" s="5" t="n"/>
-      <c r="M47" s="5" t="n"/>
-      <c r="N47" s="5" t="n"/>
-      <c r="O47" s="5" t="n"/>
-      <c r="P47" s="11" t="n"/>
-      <c r="Q47" s="5" t="n"/>
-      <c r="R47" s="5" t="n"/>
-      <c r="S47" s="5" t="n"/>
-      <c r="T47" s="11" t="n"/>
-      <c r="U47" s="5" t="n"/>
-      <c r="V47" s="5" t="n"/>
-      <c r="W47" s="5" t="n"/>
-      <c r="X47" s="5" t="n"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="11" t="n"/>
-      <c r="B48" s="5" t="n"/>
-      <c r="C48" s="5" t="n"/>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
-      <c r="H48" s="5" t="n"/>
-      <c r="I48" s="5" t="n"/>
-      <c r="J48" s="5" t="n"/>
-      <c r="K48" s="5" t="n"/>
-      <c r="L48" s="5" t="n"/>
-      <c r="M48" s="5" t="n"/>
-      <c r="N48" s="5" t="n"/>
-      <c r="O48" s="5" t="n"/>
-      <c r="P48" s="11" t="n"/>
-      <c r="Q48" s="5" t="n"/>
-      <c r="R48" s="5" t="n"/>
-      <c r="S48" s="5" t="n"/>
-      <c r="T48" s="11" t="n"/>
-      <c r="U48" s="5" t="n"/>
-      <c r="V48" s="5" t="n"/>
-      <c r="W48" s="5" t="n"/>
-      <c r="X48" s="5" t="n"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="11" t="n"/>
-      <c r="B49" s="5" t="n"/>
-      <c r="C49" s="5" t="n"/>
-      <c r="D49" s="5" t="n"/>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="5" t="n"/>
-      <c r="G49" s="5" t="n"/>
-      <c r="H49" s="5" t="n"/>
-      <c r="I49" s="5" t="n"/>
-      <c r="J49" s="5" t="n"/>
-      <c r="K49" s="5" t="n"/>
-      <c r="L49" s="5" t="n"/>
-      <c r="M49" s="5" t="n"/>
-      <c r="N49" s="5" t="n"/>
-      <c r="O49" s="5" t="n"/>
-      <c r="P49" s="11" t="n"/>
-      <c r="Q49" s="5" t="n"/>
-      <c r="R49" s="5" t="n"/>
-      <c r="S49" s="5" t="n"/>
-      <c r="T49" s="11" t="n"/>
-      <c r="U49" s="5" t="n"/>
-      <c r="V49" s="5" t="n"/>
-      <c r="W49" s="5" t="n"/>
-      <c r="X49" s="5" t="n"/>
-    </row>
-    <row r="50" ht="6" customHeight="1"/>
-    <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>■ 문제점 · 건의사항</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="6" customHeight="1"/>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="10" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="5" t="n"/>
-      <c r="I53" s="5" t="n"/>
-      <c r="J53" s="5" t="n"/>
-      <c r="K53" s="5" t="n"/>
-      <c r="L53" s="5" t="n"/>
-      <c r="M53" s="5" t="n"/>
-      <c r="N53" s="5" t="n"/>
-      <c r="O53" s="5" t="n"/>
-      <c r="P53" s="5" t="n"/>
-      <c r="Q53" s="5" t="n"/>
-      <c r="R53" s="10" t="inlineStr">
-        <is>
-          <t>조치 방향</t>
-        </is>
-      </c>
-      <c r="S53" s="5" t="n"/>
-      <c r="T53" s="5" t="n"/>
-      <c r="U53" s="5" t="n"/>
-      <c r="V53" s="5" t="n"/>
-      <c r="W53" s="5" t="n"/>
-      <c r="X53" s="5" t="n"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>공정</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="n"/>
-      <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="12" t="inlineStr">
-        <is>
-          <t>7월 호우로 배수공 2.3%p 지연</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="n"/>
-      <c r="O54" s="5" t="n"/>
-      <c r="P54" s="5" t="n"/>
-      <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="12" t="inlineStr">
-        <is>
-          <t>10월 2개 조 투입으로 만회</t>
-        </is>
-      </c>
-      <c r="S54" s="5" t="n"/>
-      <c r="T54" s="5" t="n"/>
-      <c r="U54" s="5" t="n"/>
-      <c r="V54" s="5" t="n"/>
-      <c r="W54" s="5" t="n"/>
-      <c r="X54" s="5" t="n"/>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>자재</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>관급 맨홀뚜껑 반입 일정 미정</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
-      <c r="K55" s="5" t="n"/>
-      <c r="L55" s="5" t="n"/>
-      <c r="M55" s="5" t="n"/>
-      <c r="N55" s="5" t="n"/>
-      <c r="O55" s="5" t="n"/>
-      <c r="P55" s="5" t="n"/>
-      <c r="Q55" s="5" t="n"/>
-      <c r="R55" s="12" t="inlineStr">
-        <is>
-          <t>발주기관에 일정 확인 요청</t>
-        </is>
-      </c>
-      <c r="S55" s="5" t="n"/>
-      <c r="T55" s="5" t="n"/>
-      <c r="U55" s="5" t="n"/>
-      <c r="V55" s="5" t="n"/>
-      <c r="W55" s="5" t="n"/>
-      <c r="X55" s="5" t="n"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="11" t="n"/>
-      <c r="B56" s="5" t="n"/>
-      <c r="C56" s="5" t="n"/>
-      <c r="D56" s="5" t="n"/>
-      <c r="E56" s="12" t="n"/>
-      <c r="F56" s="5" t="n"/>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="n"/>
-      <c r="O56" s="5" t="n"/>
-      <c r="P56" s="5" t="n"/>
-      <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="12" t="n"/>
-      <c r="S56" s="5" t="n"/>
-      <c r="T56" s="5" t="n"/>
-      <c r="U56" s="5" t="n"/>
-      <c r="V56" s="5" t="n"/>
-      <c r="W56" s="5" t="n"/>
-      <c r="X56" s="5" t="n"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="11" t="n"/>
-      <c r="B57" s="5" t="n"/>
-      <c r="C57" s="5" t="n"/>
-      <c r="D57" s="5" t="n"/>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="5" t="n"/>
-      <c r="G57" s="5" t="n"/>
-      <c r="H57" s="5" t="n"/>
-      <c r="I57" s="5" t="n"/>
-      <c r="J57" s="5" t="n"/>
-      <c r="K57" s="5" t="n"/>
-      <c r="L57" s="5" t="n"/>
-      <c r="M57" s="5" t="n"/>
-      <c r="N57" s="5" t="n"/>
-      <c r="O57" s="5" t="n"/>
-      <c r="P57" s="5" t="n"/>
-      <c r="Q57" s="5" t="n"/>
-      <c r="R57" s="12" t="n"/>
-      <c r="S57" s="5" t="n"/>
-      <c r="T57" s="5" t="n"/>
-      <c r="U57" s="5" t="n"/>
-      <c r="V57" s="5" t="n"/>
-      <c r="W57" s="5" t="n"/>
-      <c r="X57" s="5" t="n"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="11" t="n"/>
-      <c r="B58" s="5" t="n"/>
-      <c r="C58" s="5" t="n"/>
-      <c r="D58" s="5" t="n"/>
-      <c r="E58" s="12" t="n"/>
-      <c r="F58" s="5" t="n"/>
-      <c r="G58" s="5" t="n"/>
-      <c r="H58" s="5" t="n"/>
-      <c r="I58" s="5" t="n"/>
-      <c r="J58" s="5" t="n"/>
-      <c r="K58" s="5" t="n"/>
-      <c r="L58" s="5" t="n"/>
-      <c r="M58" s="5" t="n"/>
-      <c r="N58" s="5" t="n"/>
-      <c r="O58" s="5" t="n"/>
-      <c r="P58" s="5" t="n"/>
-      <c r="Q58" s="5" t="n"/>
-      <c r="R58" s="12" t="n"/>
-      <c r="S58" s="5" t="n"/>
-      <c r="T58" s="5" t="n"/>
-      <c r="U58" s="5" t="n"/>
-      <c r="V58" s="5" t="n"/>
-      <c r="W58" s="5" t="n"/>
-      <c r="X58" s="5" t="n"/>
-    </row>
-    <row r="59" ht="6" customHeight="1"/>
-    <row r="60" ht="10" customHeight="1"/>
-    <row r="61" ht="26" customHeight="1">
-      <c r="A61" s="13" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="14" t="inlineStr"/>
-      <c r="K62" s="15" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q62" s="16" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U62" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="24" customHeight="1">
-      <c r="A63" s="14" t="inlineStr"/>
-      <c r="K63" s="15" t="inlineStr">
-        <is>
-          <t>감독(감리)</t>
-        </is>
-      </c>
-      <c r="Q63" s="16" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="U63" s="17" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="6" customHeight="1"/>
-    <row r="66" ht="19.5" customHeight="1">
-      <c r="A66" s="18" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="177">
-    <mergeCell ref="E47:O47"/>
-    <mergeCell ref="N33:P33"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="R56:X56"/>
-    <mergeCell ref="U29:X29"/>
-    <mergeCell ref="U23:X23"/>
-    <mergeCell ref="E34:M34"/>
-    <mergeCell ref="P42:S42"/>
-    <mergeCell ref="E54:Q54"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A63:J63"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="R58:X58"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="U31:X31"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="E36:M36"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="Q62:T62"/>
-    <mergeCell ref="N30:P30"/>
-    <mergeCell ref="P44:S44"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="E22:M22"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="K62:P62"/>
-    <mergeCell ref="E49:O49"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="P46:S46"/>
-    <mergeCell ref="E45:O45"/>
-    <mergeCell ref="U25:X25"/>
-    <mergeCell ref="Q63:T63"/>
-    <mergeCell ref="G12:X12"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="Q35:T35"/>
-    <mergeCell ref="N32:P32"/>
-    <mergeCell ref="P48:S48"/>
-    <mergeCell ref="Q34:T34"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="Q36:T36"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="Q30:T30"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="P47:S47"/>
-    <mergeCell ref="A53:D53"/>
-    <mergeCell ref="Q17:T17"/>
-    <mergeCell ref="P43:S43"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="A66:X66"/>
-    <mergeCell ref="E48:O48"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="U22:X22"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="N34:P34"/>
-    <mergeCell ref="E25:M25"/>
-    <mergeCell ref="R57:X57"/>
-    <mergeCell ref="N36:P36"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="E18:M18"/>
-    <mergeCell ref="Q29:T29"/>
-    <mergeCell ref="G8:X8"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="Q23:T23"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="Q31:T31"/>
-    <mergeCell ref="G11:X11"/>
-    <mergeCell ref="A15:X15"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="A51:X51"/>
-    <mergeCell ref="T46:X46"/>
-    <mergeCell ref="A61:X61"/>
-    <mergeCell ref="E20:M20"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="U24:X24"/>
-    <mergeCell ref="U18:X18"/>
-    <mergeCell ref="E29:M29"/>
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="K63:P63"/>
-    <mergeCell ref="R54:X54"/>
-    <mergeCell ref="T48:X48"/>
-    <mergeCell ref="R53:X53"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="G13:X13"/>
-    <mergeCell ref="E31:M31"/>
-    <mergeCell ref="T45:X45"/>
-    <mergeCell ref="T42:X42"/>
-    <mergeCell ref="A27:X27"/>
-    <mergeCell ref="T47:X47"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="E53:Q53"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="T44:X44"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="E55:Q55"/>
-    <mergeCell ref="P41:S41"/>
-    <mergeCell ref="E32:M32"/>
-    <mergeCell ref="U36:X36"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="T41:X41"/>
-    <mergeCell ref="N35:P35"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="P49:S49"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="E24:M24"/>
-    <mergeCell ref="N25:P25"/>
-    <mergeCell ref="A39:X39"/>
-    <mergeCell ref="E33:M33"/>
-    <mergeCell ref="U37:X37"/>
-    <mergeCell ref="T43:X43"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="E41:O41"/>
-    <mergeCell ref="E17:M17"/>
-    <mergeCell ref="U21:X21"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="E35:M35"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="U62:X62"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="E43:O43"/>
-    <mergeCell ref="E19:M19"/>
-    <mergeCell ref="E57:Q57"/>
-    <mergeCell ref="T49:X49"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="E42:O42"/>
-    <mergeCell ref="Q32:T32"/>
-    <mergeCell ref="E30:M30"/>
-    <mergeCell ref="N29:P29"/>
-    <mergeCell ref="U63:X63"/>
-    <mergeCell ref="P45:S45"/>
-    <mergeCell ref="U35:X35"/>
-    <mergeCell ref="E44:O44"/>
-    <mergeCell ref="E56:Q56"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="Q25:T25"/>
-    <mergeCell ref="E58:Q58"/>
-    <mergeCell ref="N31:P31"/>
-    <mergeCell ref="U34:X34"/>
-    <mergeCell ref="Q24:T24"/>
-    <mergeCell ref="Q18:T18"/>
-    <mergeCell ref="Q33:T33"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="E37:M37"/>
-    <mergeCell ref="U30:X30"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="E46:O46"/>
-    <mergeCell ref="E21:M21"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E23:M23"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="R55:X55"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="Q22:T22"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/wolgan-bogoseo.xlsx
+++ b/web/public/forms/wolgan-bogoseo.xlsx
@@ -576,7 +576,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
